--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T07:34:30+00:00</t>
+    <t>2026-08-20T12:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:29:44+00:00</t>
+    <t>2026-08-26T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T09:51:04+00:00</t>
+    <t>2026-09-07T07:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:55:47+00:00</t>
+    <t>2026-09-07T08:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T08:13:14+00:00</t>
+    <t>2026-09-07T09:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:57:01+00:00</t>
+    <t>2026-09-07T11:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:48:24+00:00</t>
+    <t>2026-09-07T13:20:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T13:20:56+00:00</t>
+    <t>2026-09-08T07:12:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
+++ b/feature/enhancements/ig/StructureDefinition-FrPractitionerRoleExerciceAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T07:12:03+00:00</t>
+    <t>2026-09-08T07:46:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
